--- a/data/trans_orig/P23_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>320323</t>
+          <t>321721</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>381175</t>
+          <t>381632</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150155</t>
+          <t>147783</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>198271</t>
+          <t>195295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>487779</t>
+          <t>484580</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>571051</t>
+          <t>565242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649506</t>
+          <t>649049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>710358</t>
+          <t>708960</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1116842</t>
+          <t>1119818</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1164958</t>
+          <t>1167330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1774742</t>
+          <t>1780551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1858014</t>
+          <t>1861213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>727420</t>
+          <t>726712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>808445</t>
+          <t>811865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>493534</t>
+          <t>495661</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>568151</t>
+          <t>568206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1242956</t>
+          <t>1244972</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1356544</t>
+          <t>1356350</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>884968</t>
+          <t>881548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>965993</t>
+          <t>966701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1019522</t>
+          <t>1019467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1094139</t>
+          <t>1092012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1924542</t>
+          <t>1924736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2038130</t>
+          <t>2036114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>162131</t>
+          <t>163797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206310</t>
+          <t>209809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107359</t>
+          <t>108580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148093</t>
+          <t>145905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284861</t>
+          <t>280573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344952</t>
+          <t>342402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>345098</t>
+          <t>341599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>389277</t>
+          <t>387611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328319</t>
+          <t>330507</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>369053</t>
+          <t>367832</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>682868</t>
+          <t>685418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>742959</t>
+          <t>747247</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1244842</t>
+          <t>1252736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1361477</t>
+          <t>1365380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>785050</t>
+          <t>781070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>885840</t>
+          <t>876985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2055957</t>
+          <t>2058038</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2216426</t>
+          <t>2217789</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1914024</t>
+          <t>1910121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2030659</t>
+          <t>2022765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2493357</t>
+          <t>2502212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2594147</t>
+          <t>2598127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4438272</t>
+          <t>4436909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4598741</t>
+          <t>4596660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>282391</t>
+          <t>285881</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>345543</t>
+          <t>344073</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>172023</t>
+          <t>170834</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>225606</t>
+          <t>222476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>472297</t>
+          <t>469586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>556850</t>
+          <t>550576</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>629100</t>
+          <t>630570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692252</t>
+          <t>688762</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1112191</t>
+          <t>1115321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1165774</t>
+          <t>1166963</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1755590</t>
+          <t>1761864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1840143</t>
+          <t>1842854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>747368</t>
+          <t>748262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>834994</t>
+          <t>831825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>583770</t>
+          <t>583198</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>661822</t>
+          <t>670806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1348676</t>
+          <t>1355763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1472770</t>
+          <t>1472522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1127934</t>
+          <t>1131103</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1215560</t>
+          <t>1214666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1093999</t>
+          <t>1085015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1172051</t>
+          <t>1172623</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2245978</t>
+          <t>2246226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2370072</t>
+          <t>2362985</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,54%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135761</t>
+          <t>137596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180922</t>
+          <t>180937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117054</t>
+          <t>116620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158049</t>
+          <t>158387</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263191</t>
+          <t>259269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322982</t>
+          <t>321209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300259</t>
+          <t>300244</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>345420</t>
+          <t>343585</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300582</t>
+          <t>300244</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341577</t>
+          <t>342011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616831</t>
+          <t>618604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>676622</t>
+          <t>680544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,41%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1198467</t>
+          <t>1200043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1314057</t>
+          <t>1314908</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>905566</t>
+          <t>906191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1014150</t>
+          <t>1014851</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2134504</t>
+          <t>2135898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2306492</t>
+          <t>2294663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2104695</t>
+          <t>2103844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2220285</t>
+          <t>2218709</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2538098</t>
+          <t>2537397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2646682</t>
+          <t>2646057</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4664508</t>
+          <t>4676337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4836496</t>
+          <t>4835102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>199866</t>
+          <t>199745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249807</t>
+          <t>248570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116721</t>
+          <t>114211</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158762</t>
+          <t>159950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>327104</t>
+          <t>323901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>393330</t>
+          <t>394300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>503675</t>
+          <t>504912</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>553616</t>
+          <t>553737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>833504</t>
+          <t>832316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>875545</t>
+          <t>878055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1352418</t>
+          <t>1351448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1418644</t>
+          <t>1421847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,45%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>763425</t>
+          <t>761085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>852246</t>
+          <t>853057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>620480</t>
+          <t>618596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>699211</t>
+          <t>701404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1410542</t>
+          <t>1406342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1529293</t>
+          <t>1531101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1224139</t>
+          <t>1223328</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1312960</t>
+          <t>1315300</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1286973</t>
+          <t>1284780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1365704</t>
+          <t>1367588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2533275</t>
+          <t>2531467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2652026</t>
+          <t>2656226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115929</t>
+          <t>115378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157933</t>
+          <t>158574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100239</t>
+          <t>101448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>139570</t>
+          <t>140069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>229525</t>
+          <t>228087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>287983</t>
+          <t>288264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387881</t>
+          <t>387240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429885</t>
+          <t>430436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408643</t>
+          <t>408144</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447974</t>
+          <t>446765</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>806044</t>
+          <t>805763</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>864502</t>
+          <t>865940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,15%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1110958</t>
+          <t>1110754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1220029</t>
+          <t>1221694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>864180</t>
+          <t>861760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>970567</t>
+          <t>970243</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2011008</t>
+          <t>1998494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2158537</t>
+          <t>2159290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2155652</t>
+          <t>2153987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2264723</t>
+          <t>2264927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2556095</t>
+          <t>2556419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2662482</t>
+          <t>2664902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4743806</t>
+          <t>4743053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4891335</t>
+          <t>4903849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122350</t>
+          <t>120868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162353</t>
+          <t>161940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67444</t>
+          <t>67092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93320</t>
+          <t>91988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197344</t>
+          <t>196478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242002</t>
+          <t>244067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352585</t>
+          <t>352998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392588</t>
+          <t>394070</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>662188</t>
+          <t>663520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>688064</t>
+          <t>688416</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1028444</t>
+          <t>1026379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1073102</t>
+          <t>1073968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>406821</t>
+          <t>430492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>679419</t>
+          <t>679356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>345271</t>
+          <t>352286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>540677</t>
+          <t>537096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>865553</t>
+          <t>840496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1188253</t>
+          <t>1188248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1608875</t>
+          <t>1608938</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1881473</t>
+          <t>1857802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1695802</t>
+          <t>1699383</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1891208</t>
+          <t>1884193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3336521</t>
+          <t>3336526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3659221</t>
+          <t>3684278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82710</t>
+          <t>84075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131050</t>
+          <t>133102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91502</t>
+          <t>90574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125185</t>
+          <t>125348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187542</t>
+          <t>186162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>248201</t>
+          <t>243512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515573</t>
+          <t>513521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>563913</t>
+          <t>562548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532716</t>
+          <t>532553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>566399</t>
+          <t>567327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1056324</t>
+          <t>1061013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1116983</t>
+          <t>1118363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658818</t>
+          <t>644246</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>926608</t>
+          <t>916288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>539985</t>
+          <t>541013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>718220</t>
+          <t>715360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1283543</t>
+          <t>1283051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1605420</t>
+          <t>1598379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2523248</t>
+          <t>2533568</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2791038</t>
+          <t>2805610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2931668</t>
+          <t>2934528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3109903</t>
+          <t>3108875</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5494325</t>
+          <t>5501366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5816202</t>
+          <t>5816694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>321721</t>
+          <t>320333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>381632</t>
+          <t>384935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>147783</t>
+          <t>148967</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195295</t>
+          <t>196911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>484580</t>
+          <t>484206</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>565242</t>
+          <t>564289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649049</t>
+          <t>645746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>708960</t>
+          <t>710348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1119818</t>
+          <t>1118202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1167330</t>
+          <t>1166146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1780551</t>
+          <t>1781504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1861213</t>
+          <t>1861587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>726712</t>
+          <t>725920</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>811865</t>
+          <t>805834</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>495661</t>
+          <t>493098</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>568206</t>
+          <t>566712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1244972</t>
+          <t>1240447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1356350</t>
+          <t>1354491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>881548</t>
+          <t>887579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>966701</t>
+          <t>967493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1019467</t>
+          <t>1020961</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1092012</t>
+          <t>1094575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1924736</t>
+          <t>1926595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2036114</t>
+          <t>2040639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163797</t>
+          <t>163372</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209809</t>
+          <t>207766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>108580</t>
+          <t>109991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145905</t>
+          <t>147299</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>280573</t>
+          <t>283093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>342402</t>
+          <t>338479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>341599</t>
+          <t>343642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>387611</t>
+          <t>388036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330507</t>
+          <t>329113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>367832</t>
+          <t>366421</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>685418</t>
+          <t>689341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>747247</t>
+          <t>744727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1252736</t>
+          <t>1249910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1365380</t>
+          <t>1361442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>781070</t>
+          <t>782094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>876985</t>
+          <t>883362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2058038</t>
+          <t>2061715</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2217789</t>
+          <t>2208510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1910121</t>
+          <t>1914059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2022765</t>
+          <t>2025591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2502212</t>
+          <t>2495835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2598127</t>
+          <t>2597103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4436909</t>
+          <t>4446188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4596660</t>
+          <t>4592983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>285881</t>
+          <t>282838</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344073</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170834</t>
+          <t>172410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>222476</t>
+          <t>224835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>469586</t>
+          <t>470571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>550576</t>
+          <t>549985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>630570</t>
+          <t>633346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>688762</t>
+          <t>691805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1115321</t>
+          <t>1112962</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1166963</t>
+          <t>1165387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1761864</t>
+          <t>1762455</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1842854</t>
+          <t>1841869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,65%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>748262</t>
+          <t>744102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>831825</t>
+          <t>834579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>583198</t>
+          <t>586930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>670806</t>
+          <t>666905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1355763</t>
+          <t>1353624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1472522</t>
+          <t>1479661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1131103</t>
+          <t>1128349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1214666</t>
+          <t>1218826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1085015</t>
+          <t>1088916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1172623</t>
+          <t>1168891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2246226</t>
+          <t>2239087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2362985</t>
+          <t>2365124</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,6%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137596</t>
+          <t>136289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180937</t>
+          <t>178167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116620</t>
+          <t>116253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158387</t>
+          <t>158675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259269</t>
+          <t>263380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321209</t>
+          <t>322061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300244</t>
+          <t>303014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>343585</t>
+          <t>344892</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300244</t>
+          <t>299956</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>342011</t>
+          <t>342378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>618604</t>
+          <t>617752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680544</t>
+          <t>676433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1200043</t>
+          <t>1200054</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1314908</t>
+          <t>1316732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>906191</t>
+          <t>902563</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1014851</t>
+          <t>1015106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2135898</t>
+          <t>2135591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2294663</t>
+          <t>2296540</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,94%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2103844</t>
+          <t>2102020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2218709</t>
+          <t>2218698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2537397</t>
+          <t>2537142</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2646057</t>
+          <t>2649685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4676337</t>
+          <t>4674460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4835102</t>
+          <t>4835409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>199745</t>
+          <t>202646</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>248570</t>
+          <t>253421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114211</t>
+          <t>116831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159950</t>
+          <t>160636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>323901</t>
+          <t>329426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>394300</t>
+          <t>396559</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>504912</t>
+          <t>500061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>553737</t>
+          <t>550836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>832316</t>
+          <t>831630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>878055</t>
+          <t>875435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1351448</t>
+          <t>1349189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1421847</t>
+          <t>1416322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,13%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>761085</t>
+          <t>761109</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>853057</t>
+          <t>848937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>618596</t>
+          <t>619601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>701404</t>
+          <t>701153</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1406342</t>
+          <t>1407671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1531101</t>
+          <t>1527795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1223328</t>
+          <t>1227448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1315300</t>
+          <t>1315276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1284780</t>
+          <t>1285031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1367588</t>
+          <t>1366583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2531467</t>
+          <t>2534773</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2656226</t>
+          <t>2654897</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,35%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115378</t>
+          <t>115355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158574</t>
+          <t>158343</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101448</t>
+          <t>103477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140069</t>
+          <t>142606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>228087</t>
+          <t>229201</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288264</t>
+          <t>285207</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>387240</t>
+          <t>387471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430436</t>
+          <t>430459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408144</t>
+          <t>405607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>446765</t>
+          <t>444736</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>805763</t>
+          <t>808820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>865940</t>
+          <t>864826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1110754</t>
+          <t>1104532</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1221694</t>
+          <t>1219393</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>861760</t>
+          <t>858570</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>970243</t>
+          <t>972637</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1998494</t>
+          <t>2012717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2159290</t>
+          <t>2160256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2153987</t>
+          <t>2156288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2264927</t>
+          <t>2271149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2556419</t>
+          <t>2554025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2664902</t>
+          <t>2668092</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4743053</t>
+          <t>4742087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4903849</t>
+          <t>4889626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>141171</t>
+          <t>152480</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120868</t>
+          <t>132685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161940</t>
+          <t>175282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>78845</t>
+          <t>86165</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67092</t>
+          <t>72315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91988</t>
+          <t>100676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>220016</t>
+          <t>238645</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>196478</t>
+          <t>215422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244067</t>
+          <t>267387</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>373767</t>
+          <t>426049</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352998</t>
+          <t>403247</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394070</t>
+          <t>445844</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>676663</t>
+          <t>735873</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>663520</t>
+          <t>721362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>688416</t>
+          <t>749723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1050430</t>
+          <t>1161922</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1026379</t>
+          <t>1133180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1073968</t>
+          <t>1185145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>589277</t>
+          <t>638318</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>430492</t>
+          <t>583978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>679356</t>
+          <t>688518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>464472</t>
+          <t>502270</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>352286</t>
+          <t>465232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>537096</t>
+          <t>543218</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1053749</t>
+          <t>1140589</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>840496</t>
+          <t>1083527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1188248</t>
+          <t>1203043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1699017</t>
+          <t>1590025</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1608938</t>
+          <t>1539825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1857802</t>
+          <t>1644365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1772007</t>
+          <t>1667714</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1699383</t>
+          <t>1626766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1884193</t>
+          <t>1704752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3471025</t>
+          <t>3257738</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3336526</t>
+          <t>3195284</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3684278</t>
+          <t>3314800</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288294</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288294</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288294</t>
+          <t>2228343</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236479</t>
+          <t>2169984</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236479</t>
+          <t>2169984</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236479</t>
+          <t>2169984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524774</t>
+          <t>4398327</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524774</t>
+          <t>4398327</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524774</t>
+          <t>4398327</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>110282</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84075</t>
+          <t>89581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133102</t>
+          <t>130340</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,27 +6258,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>107408</t>
+          <t>117389</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90574</t>
+          <t>100679</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125348</t>
+          <t>139501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>210850</t>
+          <t>227671</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186162</t>
+          <t>199708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243512</t>
+          <t>256975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>543181</t>
+          <t>601305</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513521</t>
+          <t>581247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>562548</t>
+          <t>622006</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,22 +6371,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>550493</t>
+          <t>615025</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532553</t>
+          <t>592913</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>567327</t>
+          <t>631735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1093675</t>
+          <t>1216330</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1061013</t>
+          <t>1187026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1118363</t>
+          <t>1244293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>657901</t>
+          <t>732414</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>657901</t>
+          <t>732414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657901</t>
+          <t>732414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1304525</t>
+          <t>1444001</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1304525</t>
+          <t>1444001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1304525</t>
+          <t>1444001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>833890</t>
+          <t>901081</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>644246</t>
+          <t>846075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>916288</t>
+          <t>959973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>650725</t>
+          <t>705824</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>541013</t>
+          <t>664337</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>715360</t>
+          <t>749268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1484616</t>
+          <t>1606904</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1283051</t>
+          <t>1538367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1598379</t>
+          <t>1677482</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2615966</t>
+          <t>2617378</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2533568</t>
+          <t>2558486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2805610</t>
+          <t>2672384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2999163</t>
+          <t>3018611</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2934528</t>
+          <t>2975167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3108875</t>
+          <t>3060098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5615129</t>
+          <t>5635991</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5501366</t>
+          <t>5565413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5816694</t>
+          <t>5704528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>78,76%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449856</t>
+          <t>3518459</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449856</t>
+          <t>3518459</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449856</t>
+          <t>3518459</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649888</t>
+          <t>3724435</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649888</t>
+          <t>3724435</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649888</t>
+          <t>3724435</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099745</t>
+          <t>7242895</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099745</t>
+          <t>7242895</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099745</t>
+          <t>7242895</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
